--- a/NewZealand/NZ_Bioinfor_Mentors_reviewed.xlsx
+++ b/NewZealand/NZ_Bioinfor_Mentors_reviewed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yanwe\Desktop\NewZealand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE08C86D-EC75-40D1-94C7-AE8B6100662F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73CA7868-A9B8-482F-AA37-CD9EA07C5BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,14 +26,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="573">
   <si>
     <t>排名</t>
   </si>
   <si>
-    <t>推荐分</t>
-  </si>
-  <si>
     <t>Bioinfo优先级</t>
   </si>
   <si>
@@ -919,9 +916,6 @@
     <t>Strong: genome/transcriptome evolution</t>
   </si>
   <si>
-    <t>https://www.otago.ac.nz/profiles/nathan-kenny</t>
-  </si>
-  <si>
     <t>Good; younger PI</t>
   </si>
   <si>
@@ -1739,6 +1733,22 @@
   </si>
   <si>
     <t>https://profiles.auckland.ac.nz/adru001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.otago.ac.nz/healthsciences/expertise/profile?id=1735</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.otago.ac.nz/biochemistry/people/profile?id=3414</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.otago.ac.nz/healthsciences/expertise/profile?id=45</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2117,14 +2127,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:U59"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
-    <col min="4" max="4" width="35" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="3" max="3" width="23.90625" customWidth="1"/>
+    <col min="4" max="4" width="30.54296875" customWidth="1"/>
+    <col min="5" max="5" width="4.453125" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
     <col min="7" max="7" width="31.453125" customWidth="1"/>
     <col min="8" max="8" width="75.7265625" customWidth="1"/>
@@ -2138,119 +2147,116 @@
     <col min="19" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>95</v>
-      </c>
       <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
         <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
       </c>
       <c r="E2">
         <v>281</v>
       </c>
       <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>24</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>25</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>26</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>27</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>28</v>
-      </c>
-      <c r="L2" t="s">
-        <v>29</v>
       </c>
       <c r="M2">
         <v>4</v>
       </c>
       <c r="N2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" t="s">
         <v>30</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>31</v>
-      </c>
-      <c r="P2" t="s">
-        <v>32</v>
       </c>
       <c r="Q2">
         <v>22</v>
@@ -2268,54 +2274,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>91</v>
-      </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3">
         <v>197</v>
       </c>
       <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
         <v>34</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>35</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>36</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>37</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>38</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>39</v>
-      </c>
-      <c r="L3" t="s">
-        <v>40</v>
       </c>
       <c r="M3">
         <v>4</v>
       </c>
       <c r="N3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" t="s">
         <v>41</v>
       </c>
-      <c r="O3" t="s">
-        <v>42</v>
-      </c>
       <c r="P3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q3">
         <v>27</v>
@@ -2338,49 +2341,49 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
         <v>43</v>
-      </c>
-      <c r="D4" t="s">
-        <v>44</v>
       </c>
       <c r="E4">
         <v>65</v>
       </c>
       <c r="F4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
         <v>45</v>
       </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>46</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>47</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>48</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>49</v>
-      </c>
-      <c r="L4" t="s">
-        <v>50</v>
       </c>
       <c r="M4">
         <v>4</v>
       </c>
       <c r="N4" t="s">
+        <v>50</v>
+      </c>
+      <c r="O4" t="s">
         <v>51</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>52</v>
-      </c>
-      <c r="P4" t="s">
-        <v>53</v>
       </c>
       <c r="Q4">
         <v>22</v>
@@ -2402,50 +2405,47 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>89</v>
-      </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5">
         <v>65</v>
       </c>
       <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" t="s">
         <v>55</v>
       </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>56</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>57</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>58</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>59</v>
-      </c>
-      <c r="L5" t="s">
-        <v>60</v>
       </c>
       <c r="M5">
         <v>4</v>
       </c>
       <c r="N5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q5">
         <v>27</v>
@@ -2463,54 +2463,54 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" t="s">
         <v>62</v>
-      </c>
-      <c r="D6" t="s">
-        <v>63</v>
       </c>
       <c r="E6">
         <v>261</v>
       </c>
       <c r="F6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" t="s">
         <v>64</v>
       </c>
-      <c r="G6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>65</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>66</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>67</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>68</v>
-      </c>
-      <c r="L6" t="s">
-        <v>69</v>
       </c>
       <c r="M6">
         <v>5</v>
       </c>
       <c r="N6" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" t="s">
         <v>70</v>
       </c>
-      <c r="O6" t="s">
-        <v>71</v>
-      </c>
       <c r="P6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q6">
         <v>27</v>
@@ -2528,54 +2528,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>88</v>
-      </c>
       <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" t="s">
         <v>72</v>
-      </c>
-      <c r="D7" t="s">
-        <v>73</v>
       </c>
       <c r="E7">
         <v>230</v>
       </c>
       <c r="F7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" t="s">
         <v>74</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>75</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>76</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>77</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>78</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>79</v>
-      </c>
-      <c r="L7" t="s">
-        <v>80</v>
       </c>
       <c r="M7">
         <v>5</v>
       </c>
       <c r="N7" t="s">
+        <v>80</v>
+      </c>
+      <c r="O7" t="s">
         <v>81</v>
       </c>
-      <c r="O7" t="s">
-        <v>82</v>
-      </c>
       <c r="P7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q7">
         <v>32</v>
@@ -2593,54 +2590,51 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8">
-        <v>88</v>
-      </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8">
         <v>197</v>
       </c>
       <c r="F8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" t="s">
         <v>83</v>
       </c>
-      <c r="G8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>84</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>85</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>86</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>87</v>
-      </c>
-      <c r="L8" t="s">
-        <v>88</v>
       </c>
       <c r="M8">
         <v>4</v>
       </c>
       <c r="N8" t="s">
+        <v>88</v>
+      </c>
+      <c r="O8" t="s">
         <v>89</v>
       </c>
-      <c r="O8" t="s">
-        <v>90</v>
-      </c>
       <c r="P8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q8">
         <v>27</v>
@@ -2663,49 +2657,49 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9">
         <v>65</v>
       </c>
       <c r="F9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" t="s">
         <v>91</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>92</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>93</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>94</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>95</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>96</v>
-      </c>
-      <c r="L9" t="s">
-        <v>97</v>
       </c>
       <c r="M9">
         <v>4</v>
       </c>
       <c r="N9" t="s">
+        <v>97</v>
+      </c>
+      <c r="O9" t="s">
         <v>98</v>
       </c>
-      <c r="O9" t="s">
-        <v>99</v>
-      </c>
       <c r="P9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q9">
         <v>32</v>
@@ -2723,54 +2717,54 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10">
         <v>197</v>
       </c>
       <c r="F10" t="s">
+        <v>99</v>
+      </c>
+      <c r="G10" t="s">
         <v>100</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>101</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>102</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>103</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>104</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>105</v>
-      </c>
-      <c r="L10" t="s">
-        <v>106</v>
       </c>
       <c r="M10">
         <v>4</v>
       </c>
       <c r="N10" t="s">
+        <v>106</v>
+      </c>
+      <c r="O10" t="s">
         <v>107</v>
       </c>
-      <c r="O10" t="s">
-        <v>108</v>
-      </c>
       <c r="P10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q10">
         <v>22</v>
@@ -2793,49 +2787,49 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E11">
         <v>65</v>
       </c>
       <c r="F11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" t="s">
         <v>110</v>
       </c>
-      <c r="G11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>111</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>112</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>113</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>114</v>
-      </c>
-      <c r="L11" t="s">
-        <v>115</v>
       </c>
       <c r="M11">
         <v>4</v>
       </c>
       <c r="N11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O11" t="s">
+        <v>51</v>
+      </c>
+      <c r="P11" t="s">
         <v>52</v>
-      </c>
-      <c r="P11" t="s">
-        <v>53</v>
       </c>
       <c r="Q11">
         <v>22</v>
@@ -2853,54 +2847,51 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12">
-        <v>85</v>
-      </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12">
         <v>197</v>
       </c>
       <c r="F12" t="s">
+        <v>117</v>
+      </c>
+      <c r="G12" t="s">
         <v>118</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>119</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>120</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>121</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>122</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
         <v>123</v>
-      </c>
-      <c r="L12" t="s">
-        <v>124</v>
       </c>
       <c r="M12">
         <v>5</v>
       </c>
       <c r="N12" t="s">
+        <v>124</v>
+      </c>
+      <c r="O12" t="s">
         <v>125</v>
       </c>
-      <c r="O12" t="s">
-        <v>126</v>
-      </c>
       <c r="P12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q12">
         <v>22</v>
@@ -2918,54 +2909,51 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13">
-        <v>84</v>
-      </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E13">
         <v>230</v>
       </c>
       <c r="F13" t="s">
+        <v>127</v>
+      </c>
+      <c r="G13" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" t="s">
         <v>128</v>
       </c>
-      <c r="G13" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>129</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>130</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>131</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
         <v>132</v>
-      </c>
-      <c r="L13" t="s">
-        <v>133</v>
       </c>
       <c r="M13">
         <v>4</v>
       </c>
       <c r="N13" t="s">
+        <v>133</v>
+      </c>
+      <c r="O13" t="s">
         <v>134</v>
       </c>
-      <c r="O13" t="s">
-        <v>135</v>
-      </c>
       <c r="P13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q13">
         <v>27</v>
@@ -2987,50 +2975,47 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14">
-        <v>84</v>
-      </c>
       <c r="C14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E14">
         <v>65</v>
       </c>
       <c r="F14" t="s">
+        <v>136</v>
+      </c>
+      <c r="G14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" t="s">
         <v>137</v>
       </c>
-      <c r="G14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>138</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>139</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>140</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
         <v>141</v>
-      </c>
-      <c r="L14" t="s">
-        <v>142</v>
       </c>
       <c r="M14">
         <v>4</v>
       </c>
       <c r="N14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O14" t="s">
+        <v>51</v>
+      </c>
+      <c r="P14" t="s">
         <v>52</v>
-      </c>
-      <c r="P14" t="s">
-        <v>53</v>
       </c>
       <c r="Q14">
         <v>22</v>
@@ -3048,54 +3033,54 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E15">
         <v>197</v>
       </c>
       <c r="F15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G15" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" t="s">
         <v>145</v>
       </c>
-      <c r="G15" t="s">
-        <v>35</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>146</v>
       </c>
-      <c r="I15" t="s">
-        <v>147</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="J15" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="K15" t="s">
         <v>148</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
         <v>149</v>
-      </c>
-      <c r="L15" t="s">
-        <v>150</v>
       </c>
       <c r="M15">
         <v>5</v>
       </c>
       <c r="N15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q15">
         <v>27</v>
@@ -3113,54 +3098,51 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16">
-        <v>83</v>
-      </c>
       <c r="C16" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" t="s">
         <v>152</v>
-      </c>
-      <c r="D16" t="s">
-        <v>153</v>
       </c>
       <c r="E16">
         <v>240</v>
       </c>
       <c r="F16" t="s">
+        <v>153</v>
+      </c>
+      <c r="G16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" t="s">
         <v>154</v>
       </c>
-      <c r="G16" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>155</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>156</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>157</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>158</v>
-      </c>
-      <c r="L16" t="s">
-        <v>159</v>
       </c>
       <c r="M16">
         <v>4</v>
       </c>
       <c r="N16" t="s">
+        <v>159</v>
+      </c>
+      <c r="O16" t="s">
         <v>160</v>
       </c>
-      <c r="O16" t="s">
-        <v>161</v>
-      </c>
       <c r="P16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q16">
         <v>22</v>
@@ -3178,54 +3160,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17">
-        <v>83</v>
-      </c>
       <c r="C17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E17">
         <v>261</v>
       </c>
       <c r="F17" t="s">
+        <v>162</v>
+      </c>
+      <c r="G17" t="s">
         <v>163</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>164</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>165</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>166</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
+        <v>67</v>
+      </c>
+      <c r="L17" t="s">
         <v>167</v>
-      </c>
-      <c r="K17" t="s">
-        <v>68</v>
-      </c>
-      <c r="L17" t="s">
-        <v>168</v>
       </c>
       <c r="M17">
         <v>4</v>
       </c>
       <c r="N17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q17">
         <v>22</v>
@@ -3247,50 +3226,47 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18">
-        <v>83</v>
-      </c>
       <c r="C18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E18">
         <v>65</v>
       </c>
       <c r="F18" t="s">
+        <v>169</v>
+      </c>
+      <c r="G18" t="s">
+        <v>118</v>
+      </c>
+      <c r="H18" t="s">
         <v>170</v>
       </c>
-      <c r="G18" t="s">
-        <v>119</v>
-      </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>171</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>172</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>173</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
         <v>174</v>
-      </c>
-      <c r="L18" t="s">
-        <v>175</v>
       </c>
       <c r="M18">
         <v>4</v>
       </c>
       <c r="N18" t="s">
+        <v>175</v>
+      </c>
+      <c r="O18" t="s">
         <v>176</v>
       </c>
-      <c r="O18" t="s">
-        <v>177</v>
-      </c>
       <c r="P18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q18">
         <v>22</v>
@@ -3308,54 +3284,54 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E19">
         <v>230</v>
       </c>
       <c r="F19" t="s">
+        <v>178</v>
+      </c>
+      <c r="G19" t="s">
         <v>179</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>180</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>181</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>182</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>183</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
         <v>184</v>
-      </c>
-      <c r="L19" t="s">
-        <v>185</v>
       </c>
       <c r="M19">
         <v>4</v>
       </c>
       <c r="N19" t="s">
+        <v>185</v>
+      </c>
+      <c r="O19" t="s">
         <v>186</v>
       </c>
-      <c r="O19" t="s">
-        <v>187</v>
-      </c>
       <c r="P19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q19">
         <v>22</v>
@@ -3377,50 +3353,47 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20">
-        <v>82</v>
-      </c>
       <c r="C20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E20">
         <v>65</v>
       </c>
       <c r="F20" t="s">
+        <v>188</v>
+      </c>
+      <c r="G20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" t="s">
         <v>189</v>
       </c>
-      <c r="G20" t="s">
-        <v>92</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>190</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="K20" t="s">
         <v>191</v>
       </c>
-      <c r="J20" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
         <v>192</v>
-      </c>
-      <c r="L20" t="s">
-        <v>193</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20" t="s">
+        <v>193</v>
+      </c>
+      <c r="O20" t="s">
         <v>194</v>
       </c>
-      <c r="O20" t="s">
-        <v>195</v>
-      </c>
       <c r="P20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q20">
         <v>32</v>
@@ -3438,54 +3411,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21">
-        <v>82</v>
-      </c>
       <c r="C21" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21">
         <v>197</v>
       </c>
       <c r="F21" t="s">
+        <v>196</v>
+      </c>
+      <c r="G21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" t="s">
         <v>197</v>
       </c>
-      <c r="G21" t="s">
-        <v>24</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>198</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>199</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>200</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
         <v>201</v>
-      </c>
-      <c r="L21" t="s">
-        <v>202</v>
       </c>
       <c r="M21">
         <v>3</v>
       </c>
       <c r="N21" t="s">
+        <v>202</v>
+      </c>
+      <c r="O21" t="s">
         <v>203</v>
       </c>
-      <c r="O21" t="s">
-        <v>204</v>
-      </c>
       <c r="P21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q21">
         <v>22</v>
@@ -3503,54 +3473,51 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22">
-        <v>80</v>
-      </c>
       <c r="C22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E22">
         <v>281</v>
       </c>
       <c r="F22" t="s">
+        <v>205</v>
+      </c>
+      <c r="G22" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" t="s">
         <v>206</v>
       </c>
-      <c r="G22" t="s">
-        <v>92</v>
-      </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>207</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>208</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>209</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>210</v>
-      </c>
-      <c r="L22" t="s">
-        <v>211</v>
       </c>
       <c r="M22">
         <v>4</v>
       </c>
       <c r="N22" t="s">
+        <v>211</v>
+      </c>
+      <c r="O22" t="s">
         <v>212</v>
       </c>
-      <c r="O22" t="s">
-        <v>213</v>
-      </c>
       <c r="P22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q22">
         <v>32</v>
@@ -3568,54 +3535,51 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23">
-        <v>80</v>
-      </c>
       <c r="C23" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E23">
         <v>230</v>
       </c>
       <c r="F23" t="s">
+        <v>214</v>
+      </c>
+      <c r="G23" t="s">
         <v>215</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>216</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>217</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>218</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
+        <v>183</v>
+      </c>
+      <c r="L23" t="s">
         <v>219</v>
-      </c>
-      <c r="K23" t="s">
-        <v>184</v>
-      </c>
-      <c r="L23" t="s">
-        <v>220</v>
       </c>
       <c r="M23">
         <v>4</v>
       </c>
       <c r="N23" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O23" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q23">
         <v>27</v>
@@ -3633,54 +3597,51 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24">
-        <v>80</v>
-      </c>
       <c r="C24" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E24">
         <v>261</v>
       </c>
       <c r="F24" t="s">
+        <v>222</v>
+      </c>
+      <c r="G24" t="s">
+        <v>34</v>
+      </c>
+      <c r="H24" t="s">
         <v>223</v>
       </c>
-      <c r="G24" t="s">
-        <v>35</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>224</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>225</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
+        <v>67</v>
+      </c>
+      <c r="L24" t="s">
         <v>226</v>
-      </c>
-      <c r="K24" t="s">
-        <v>68</v>
-      </c>
-      <c r="L24" t="s">
-        <v>227</v>
       </c>
       <c r="M24">
         <v>4</v>
       </c>
       <c r="N24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q24">
         <v>27</v>
@@ -3698,54 +3659,51 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25">
-        <v>80</v>
-      </c>
       <c r="C25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E25">
         <v>197</v>
       </c>
       <c r="F25" t="s">
+        <v>229</v>
+      </c>
+      <c r="G25" t="s">
         <v>230</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>231</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>232</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>233</v>
       </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>234</v>
       </c>
-      <c r="K25" t="s">
+      <c r="L25" t="s">
         <v>235</v>
-      </c>
-      <c r="L25" t="s">
-        <v>236</v>
       </c>
       <c r="M25">
         <v>3</v>
       </c>
       <c r="N25" t="s">
+        <v>236</v>
+      </c>
+      <c r="O25" t="s">
         <v>237</v>
       </c>
-      <c r="O25" t="s">
-        <v>238</v>
-      </c>
       <c r="P25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -3763,54 +3721,51 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26">
-        <v>79</v>
-      </c>
       <c r="C26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E26">
         <v>230</v>
       </c>
       <c r="F26" t="s">
+        <v>238</v>
+      </c>
+      <c r="G26" t="s">
+        <v>91</v>
+      </c>
+      <c r="H26" t="s">
         <v>239</v>
       </c>
-      <c r="G26" t="s">
-        <v>92</v>
-      </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>240</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>241</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
+        <v>95</v>
+      </c>
+      <c r="L26" t="s">
         <v>242</v>
-      </c>
-      <c r="K26" t="s">
-        <v>96</v>
-      </c>
-      <c r="L26" t="s">
-        <v>243</v>
       </c>
       <c r="M26">
         <v>5</v>
       </c>
       <c r="N26" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q26">
         <v>32</v>
@@ -3828,54 +3783,51 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27">
-        <v>78</v>
-      </c>
       <c r="C27" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E27">
         <v>261</v>
       </c>
       <c r="F27" t="s">
+        <v>244</v>
+      </c>
+      <c r="G27" t="s">
+        <v>163</v>
+      </c>
+      <c r="H27" t="s">
         <v>245</v>
       </c>
-      <c r="G27" t="s">
-        <v>164</v>
-      </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>246</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>247</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
+        <v>67</v>
+      </c>
+      <c r="L27" t="s">
         <v>248</v>
-      </c>
-      <c r="K27" t="s">
-        <v>68</v>
-      </c>
-      <c r="L27" t="s">
-        <v>249</v>
       </c>
       <c r="M27">
         <v>4</v>
       </c>
       <c r="N27" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q27">
         <v>22</v>
@@ -3897,50 +3849,47 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28">
-        <v>78</v>
-      </c>
       <c r="C28" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E28">
         <v>65</v>
       </c>
       <c r="F28" t="s">
+        <v>251</v>
+      </c>
+      <c r="G28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H28" t="s">
         <v>252</v>
       </c>
-      <c r="G28" t="s">
-        <v>35</v>
-      </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>253</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>254</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>255</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L28" t="s">
         <v>256</v>
-      </c>
-      <c r="L28" t="s">
-        <v>257</v>
       </c>
       <c r="M28">
         <v>4</v>
       </c>
       <c r="N28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O28" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q28">
         <v>27</v>
@@ -3958,54 +3907,51 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29">
-        <v>77</v>
-      </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E29">
         <v>197</v>
       </c>
       <c r="F29" t="s">
+        <v>259</v>
+      </c>
+      <c r="G29" t="s">
         <v>260</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>261</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>262</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>263</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>264</v>
       </c>
-      <c r="K29" t="s">
+      <c r="L29" t="s">
         <v>265</v>
-      </c>
-      <c r="L29" t="s">
-        <v>266</v>
       </c>
       <c r="M29">
         <v>5</v>
       </c>
       <c r="N29" t="s">
+        <v>266</v>
+      </c>
+      <c r="O29" t="s">
         <v>267</v>
       </c>
-      <c r="O29" t="s">
-        <v>268</v>
-      </c>
       <c r="P29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q29">
         <v>35</v>
@@ -4023,54 +3969,54 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E30">
         <v>261</v>
       </c>
       <c r="F30" t="s">
+        <v>269</v>
+      </c>
+      <c r="G30" t="s">
+        <v>91</v>
+      </c>
+      <c r="H30" t="s">
         <v>270</v>
       </c>
-      <c r="G30" t="s">
-        <v>92</v>
-      </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
         <v>271</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
         <v>272</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
+        <v>67</v>
+      </c>
+      <c r="L30" t="s">
         <v>273</v>
-      </c>
-      <c r="K30" t="s">
-        <v>68</v>
-      </c>
-      <c r="L30" t="s">
-        <v>274</v>
       </c>
       <c r="M30">
         <v>4</v>
       </c>
       <c r="N30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q30">
         <v>32</v>
@@ -4088,54 +4034,51 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31">
-        <v>76</v>
-      </c>
       <c r="C31" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E31">
         <v>230</v>
       </c>
       <c r="F31" t="s">
+        <v>276</v>
+      </c>
+      <c r="G31" t="s">
         <v>277</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>278</v>
       </c>
-      <c r="H31" t="s">
+      <c r="I31" t="s">
         <v>279</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>280</v>
       </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
+        <v>183</v>
+      </c>
+      <c r="L31" t="s">
         <v>281</v>
-      </c>
-      <c r="K31" t="s">
-        <v>184</v>
-      </c>
-      <c r="L31" t="s">
-        <v>282</v>
       </c>
       <c r="M31">
         <v>4</v>
       </c>
       <c r="N31" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O31" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q31">
         <v>22</v>
@@ -4157,50 +4100,47 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32">
-        <v>76</v>
-      </c>
       <c r="C32" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E32">
         <v>65</v>
       </c>
       <c r="F32" t="s">
+        <v>284</v>
+      </c>
+      <c r="G32" t="s">
+        <v>34</v>
+      </c>
+      <c r="H32" t="s">
         <v>285</v>
       </c>
-      <c r="G32" t="s">
-        <v>35</v>
-      </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>286</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>287</v>
       </c>
-      <c r="J32" t="s">
+      <c r="K32" t="s">
         <v>288</v>
       </c>
-      <c r="K32" t="s">
+      <c r="L32" t="s">
         <v>289</v>
-      </c>
-      <c r="L32" t="s">
-        <v>290</v>
       </c>
       <c r="M32">
         <v>4</v>
       </c>
       <c r="N32" t="s">
+        <v>290</v>
+      </c>
+      <c r="O32" t="s">
         <v>291</v>
       </c>
-      <c r="O32" t="s">
-        <v>292</v>
-      </c>
       <c r="P32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q32">
         <v>27</v>
@@ -4218,54 +4158,54 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E33">
         <v>197</v>
       </c>
       <c r="F33" t="s">
+        <v>293</v>
+      </c>
+      <c r="G33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" t="s">
         <v>294</v>
       </c>
-      <c r="G33" t="s">
-        <v>24</v>
-      </c>
-      <c r="H33" t="s">
+      <c r="I33" t="s">
         <v>295</v>
       </c>
-      <c r="I33" t="s">
+      <c r="J33" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="K33" t="s">
         <v>296</v>
       </c>
-      <c r="J33" t="s">
+      <c r="L33" t="s">
         <v>297</v>
-      </c>
-      <c r="K33" t="s">
-        <v>298</v>
-      </c>
-      <c r="L33" t="s">
-        <v>299</v>
       </c>
       <c r="M33">
         <v>3</v>
       </c>
       <c r="N33" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="O33" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="P33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q33">
         <v>22</v>
@@ -4287,50 +4227,47 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34">
-        <v>75</v>
-      </c>
       <c r="C34" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E34">
         <v>65</v>
       </c>
       <c r="F34" t="s">
+        <v>301</v>
+      </c>
+      <c r="G34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" t="s">
+        <v>302</v>
+      </c>
+      <c r="I34" t="s">
         <v>303</v>
       </c>
-      <c r="G34" t="s">
-        <v>24</v>
-      </c>
-      <c r="H34" t="s">
+      <c r="J34" t="s">
         <v>304</v>
       </c>
-      <c r="I34" t="s">
+      <c r="K34" t="s">
         <v>305</v>
       </c>
-      <c r="J34" t="s">
+      <c r="L34" t="s">
         <v>306</v>
-      </c>
-      <c r="K34" t="s">
-        <v>307</v>
-      </c>
-      <c r="L34" t="s">
-        <v>308</v>
       </c>
       <c r="M34">
         <v>3</v>
       </c>
       <c r="N34" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="O34" t="s">
+        <v>51</v>
+      </c>
+      <c r="P34" t="s">
         <v>52</v>
-      </c>
-      <c r="P34" t="s">
-        <v>53</v>
       </c>
       <c r="Q34">
         <v>22</v>
@@ -4348,54 +4285,54 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E35">
         <v>261</v>
       </c>
       <c r="F35" t="s">
+        <v>309</v>
+      </c>
+      <c r="G35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H35" t="s">
+        <v>310</v>
+      </c>
+      <c r="I35" t="s">
         <v>311</v>
       </c>
-      <c r="G35" t="s">
-        <v>92</v>
-      </c>
-      <c r="H35" t="s">
+      <c r="J35" t="s">
         <v>312</v>
       </c>
-      <c r="I35" t="s">
+      <c r="K35" t="s">
+        <v>67</v>
+      </c>
+      <c r="L35" t="s">
         <v>313</v>
-      </c>
-      <c r="J35" t="s">
-        <v>314</v>
-      </c>
-      <c r="K35" t="s">
-        <v>68</v>
-      </c>
-      <c r="L35" t="s">
-        <v>315</v>
       </c>
       <c r="M35">
         <v>4</v>
       </c>
       <c r="N35" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="O35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q35">
         <v>32</v>
@@ -4418,49 +4355,49 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E36">
         <v>65</v>
       </c>
       <c r="F36" t="s">
+        <v>316</v>
+      </c>
+      <c r="G36" t="s">
+        <v>91</v>
+      </c>
+      <c r="H36" t="s">
+        <v>317</v>
+      </c>
+      <c r="I36" t="s">
         <v>318</v>
       </c>
-      <c r="G36" t="s">
-        <v>92</v>
-      </c>
-      <c r="H36" t="s">
+      <c r="J36" t="s">
         <v>319</v>
       </c>
-      <c r="I36" t="s">
+      <c r="K36" t="s">
+        <v>95</v>
+      </c>
+      <c r="L36" t="s">
         <v>320</v>
-      </c>
-      <c r="J36" t="s">
-        <v>321</v>
-      </c>
-      <c r="K36" t="s">
-        <v>96</v>
-      </c>
-      <c r="L36" t="s">
-        <v>322</v>
       </c>
       <c r="M36">
         <v>5</v>
       </c>
       <c r="N36" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="O36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q36">
         <v>32</v>
@@ -4483,49 +4420,49 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E37">
         <v>65</v>
       </c>
       <c r="F37" t="s">
+        <v>323</v>
+      </c>
+      <c r="G37" t="s">
+        <v>91</v>
+      </c>
+      <c r="H37" t="s">
+        <v>324</v>
+      </c>
+      <c r="I37" t="s">
         <v>325</v>
       </c>
-      <c r="G37" t="s">
-        <v>92</v>
-      </c>
-      <c r="H37" t="s">
+      <c r="J37" t="s">
         <v>326</v>
       </c>
-      <c r="I37" t="s">
+      <c r="K37" t="s">
         <v>327</v>
       </c>
-      <c r="J37" t="s">
+      <c r="L37" t="s">
         <v>328</v>
-      </c>
-      <c r="K37" t="s">
-        <v>329</v>
-      </c>
-      <c r="L37" t="s">
-        <v>330</v>
       </c>
       <c r="M37">
         <v>5</v>
       </c>
       <c r="N37" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="O37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q37">
         <v>32</v>
@@ -4543,54 +4480,54 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>330</v>
+      </c>
+      <c r="D38" t="s">
         <v>72</v>
-      </c>
-      <c r="C38" t="s">
-        <v>332</v>
-      </c>
-      <c r="D38" t="s">
-        <v>73</v>
       </c>
       <c r="E38">
         <v>230</v>
       </c>
       <c r="F38" t="s">
+        <v>331</v>
+      </c>
+      <c r="G38" t="s">
+        <v>332</v>
+      </c>
+      <c r="H38" t="s">
         <v>333</v>
       </c>
-      <c r="G38" t="s">
+      <c r="I38" t="s">
         <v>334</v>
       </c>
-      <c r="H38" t="s">
+      <c r="J38" t="s">
         <v>335</v>
       </c>
-      <c r="I38" t="s">
+      <c r="K38" t="s">
         <v>336</v>
       </c>
-      <c r="J38" t="s">
+      <c r="L38" t="s">
         <v>337</v>
-      </c>
-      <c r="K38" t="s">
-        <v>338</v>
-      </c>
-      <c r="L38" t="s">
-        <v>339</v>
       </c>
       <c r="M38">
         <v>3</v>
       </c>
       <c r="N38" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="O38" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="P38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q38">
         <v>22</v>
@@ -4612,50 +4549,47 @@
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39">
-        <v>70</v>
-      </c>
       <c r="C39" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E39">
         <v>65</v>
       </c>
       <c r="F39" t="s">
+        <v>341</v>
+      </c>
+      <c r="G39" t="s">
+        <v>342</v>
+      </c>
+      <c r="H39" t="s">
         <v>343</v>
       </c>
-      <c r="G39" t="s">
+      <c r="I39" t="s">
         <v>344</v>
       </c>
-      <c r="H39" t="s">
+      <c r="J39" t="s">
         <v>345</v>
       </c>
-      <c r="I39" t="s">
+      <c r="K39" t="s">
         <v>346</v>
       </c>
-      <c r="J39" t="s">
+      <c r="L39" t="s">
         <v>347</v>
-      </c>
-      <c r="K39" t="s">
-        <v>348</v>
-      </c>
-      <c r="L39" t="s">
-        <v>349</v>
       </c>
       <c r="M39">
         <v>4</v>
       </c>
       <c r="N39" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="O39" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="P39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q39">
         <v>22</v>
@@ -4673,54 +4607,51 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40">
-        <v>68</v>
-      </c>
       <c r="C40" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E40">
         <v>197</v>
       </c>
       <c r="F40" t="s">
+        <v>350</v>
+      </c>
+      <c r="G40" t="s">
+        <v>34</v>
+      </c>
+      <c r="H40" t="s">
+        <v>351</v>
+      </c>
+      <c r="I40" t="s">
         <v>352</v>
       </c>
-      <c r="G40" t="s">
-        <v>35</v>
-      </c>
-      <c r="H40" t="s">
+      <c r="J40" t="s">
         <v>353</v>
       </c>
-      <c r="I40" t="s">
+      <c r="K40" t="s">
         <v>354</v>
       </c>
-      <c r="J40" t="s">
+      <c r="L40" t="s">
         <v>355</v>
-      </c>
-      <c r="K40" t="s">
-        <v>356</v>
-      </c>
-      <c r="L40" t="s">
-        <v>357</v>
       </c>
       <c r="M40">
         <v>4</v>
       </c>
       <c r="N40" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="O40" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q40">
         <v>27</v>
@@ -4742,50 +4673,47 @@
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41">
-        <v>68</v>
-      </c>
       <c r="C41" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E41">
         <v>65</v>
       </c>
       <c r="F41" t="s">
+        <v>358</v>
+      </c>
+      <c r="G41" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" t="s">
+        <v>359</v>
+      </c>
+      <c r="I41" t="s">
         <v>360</v>
       </c>
-      <c r="G41" t="s">
-        <v>24</v>
-      </c>
-      <c r="H41" t="s">
+      <c r="J41" t="s">
         <v>361</v>
       </c>
-      <c r="I41" t="s">
+      <c r="K41" t="s">
         <v>362</v>
       </c>
-      <c r="J41" t="s">
+      <c r="L41" t="s">
         <v>363</v>
-      </c>
-      <c r="K41" t="s">
-        <v>364</v>
-      </c>
-      <c r="L41" t="s">
-        <v>365</v>
       </c>
       <c r="M41">
         <v>3</v>
       </c>
       <c r="N41" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="O41" t="s">
+        <v>51</v>
+      </c>
+      <c r="P41" t="s">
         <v>52</v>
-      </c>
-      <c r="P41" t="s">
-        <v>53</v>
       </c>
       <c r="Q41">
         <v>22</v>
@@ -4803,54 +4731,54 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E42">
         <v>197</v>
       </c>
       <c r="F42" t="s">
+        <v>365</v>
+      </c>
+      <c r="G42" t="s">
+        <v>366</v>
+      </c>
+      <c r="H42" t="s">
         <v>367</v>
       </c>
-      <c r="G42" t="s">
+      <c r="I42" t="s">
         <v>368</v>
       </c>
-      <c r="H42" t="s">
+      <c r="J42" t="s">
         <v>369</v>
       </c>
-      <c r="I42" t="s">
+      <c r="K42" t="s">
         <v>370</v>
       </c>
-      <c r="J42" t="s">
+      <c r="L42" t="s">
         <v>371</v>
-      </c>
-      <c r="K42" t="s">
-        <v>372</v>
-      </c>
-      <c r="L42" t="s">
-        <v>373</v>
       </c>
       <c r="M42">
         <v>5</v>
       </c>
       <c r="N42" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="O42" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q42">
         <v>35</v>
@@ -4868,54 +4796,51 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43">
-        <v>66</v>
-      </c>
       <c r="C43" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D43" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E43">
         <v>240</v>
       </c>
       <c r="F43" t="s">
+        <v>373</v>
+      </c>
+      <c r="G43" t="s">
+        <v>91</v>
+      </c>
+      <c r="H43" t="s">
+        <v>374</v>
+      </c>
+      <c r="I43" t="s">
         <v>375</v>
       </c>
-      <c r="G43" t="s">
-        <v>92</v>
-      </c>
-      <c r="H43" t="s">
+      <c r="J43" t="s">
         <v>376</v>
       </c>
-      <c r="I43" t="s">
+      <c r="K43" t="s">
         <v>377</v>
       </c>
-      <c r="J43" t="s">
-        <v>378</v>
-      </c>
-      <c r="K43" t="s">
-        <v>379</v>
-      </c>
       <c r="L43" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="M43">
         <v>3</v>
       </c>
       <c r="N43" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="O43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q43">
         <v>32</v>
@@ -4933,54 +4858,54 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E44">
         <v>230</v>
       </c>
       <c r="F44" t="s">
+        <v>380</v>
+      </c>
+      <c r="G44" t="s">
+        <v>381</v>
+      </c>
+      <c r="H44" t="s">
         <v>382</v>
       </c>
-      <c r="G44" t="s">
+      <c r="I44" t="s">
         <v>383</v>
       </c>
-      <c r="H44" t="s">
+      <c r="J44" t="s">
         <v>384</v>
       </c>
-      <c r="I44" t="s">
+      <c r="K44" t="s">
         <v>385</v>
       </c>
-      <c r="J44" t="s">
+      <c r="L44" t="s">
         <v>386</v>
-      </c>
-      <c r="K44" t="s">
-        <v>387</v>
-      </c>
-      <c r="L44" t="s">
-        <v>388</v>
       </c>
       <c r="M44">
         <v>3</v>
       </c>
       <c r="N44" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="O44" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="P44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q44">
         <v>27</v>
@@ -4998,54 +4923,51 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45">
-        <v>64</v>
-      </c>
       <c r="C45" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E45">
         <v>281</v>
       </c>
       <c r="F45" t="s">
+        <v>389</v>
+      </c>
+      <c r="G45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H45" t="s">
+        <v>390</v>
+      </c>
+      <c r="I45" t="s">
         <v>391</v>
       </c>
-      <c r="G45" t="s">
-        <v>92</v>
-      </c>
-      <c r="H45" t="s">
+      <c r="J45" t="s">
         <v>392</v>
       </c>
-      <c r="I45" t="s">
+      <c r="K45" t="s">
         <v>393</v>
       </c>
-      <c r="J45" t="s">
-        <v>394</v>
-      </c>
-      <c r="K45" t="s">
-        <v>395</v>
-      </c>
       <c r="L45" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M45">
         <v>5</v>
       </c>
       <c r="N45" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="O45" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="P45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q45">
         <v>32</v>
@@ -5067,50 +4989,47 @@
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46">
-        <v>64</v>
-      </c>
       <c r="C46" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D46" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E46">
         <v>65</v>
       </c>
       <c r="F46" t="s">
+        <v>397</v>
+      </c>
+      <c r="G46" t="s">
+        <v>398</v>
+      </c>
+      <c r="H46" t="s">
         <v>399</v>
       </c>
-      <c r="G46" t="s">
+      <c r="I46" t="s">
         <v>400</v>
       </c>
-      <c r="H46" t="s">
+      <c r="J46" t="s">
         <v>401</v>
       </c>
-      <c r="I46" t="s">
+      <c r="K46" t="s">
         <v>402</v>
       </c>
-      <c r="J46" t="s">
+      <c r="L46" t="s">
         <v>403</v>
-      </c>
-      <c r="K46" t="s">
-        <v>404</v>
-      </c>
-      <c r="L46" t="s">
-        <v>405</v>
       </c>
       <c r="M46">
         <v>4</v>
       </c>
       <c r="N46" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="O46" t="s">
+        <v>51</v>
+      </c>
+      <c r="P46" t="s">
         <v>52</v>
-      </c>
-      <c r="P46" t="s">
-        <v>53</v>
       </c>
       <c r="Q46">
         <v>35</v>
@@ -5132,50 +5051,47 @@
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47">
-        <v>62</v>
-      </c>
       <c r="C47" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D47" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E47">
         <v>65</v>
       </c>
       <c r="F47" t="s">
+        <v>405</v>
+      </c>
+      <c r="G47" t="s">
+        <v>34</v>
+      </c>
+      <c r="H47" t="s">
+        <v>406</v>
+      </c>
+      <c r="I47" t="s">
         <v>407</v>
       </c>
-      <c r="G47" t="s">
-        <v>35</v>
-      </c>
-      <c r="H47" t="s">
+      <c r="J47" t="s">
         <v>408</v>
       </c>
-      <c r="I47" t="s">
+      <c r="K47" t="s">
         <v>409</v>
       </c>
-      <c r="J47" t="s">
+      <c r="L47" t="s">
         <v>410</v>
-      </c>
-      <c r="K47" t="s">
-        <v>411</v>
-      </c>
-      <c r="L47" t="s">
-        <v>412</v>
       </c>
       <c r="M47">
         <v>3</v>
       </c>
       <c r="N47" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="O47" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q47">
         <v>27</v>
@@ -5193,54 +5109,54 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E48">
         <v>197</v>
       </c>
       <c r="F48" t="s">
+        <v>414</v>
+      </c>
+      <c r="G48" t="s">
+        <v>415</v>
+      </c>
+      <c r="H48" t="s">
         <v>416</v>
       </c>
-      <c r="G48" t="s">
+      <c r="I48" t="s">
         <v>417</v>
       </c>
-      <c r="H48" t="s">
-        <v>418</v>
-      </c>
-      <c r="I48" t="s">
+      <c r="J48" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="K48" t="s">
         <v>419</v>
       </c>
-      <c r="J48" t="s">
+      <c r="L48" t="s">
         <v>420</v>
-      </c>
-      <c r="K48" t="s">
-        <v>421</v>
-      </c>
-      <c r="L48" t="s">
-        <v>422</v>
       </c>
       <c r="M48">
         <v>2</v>
       </c>
       <c r="N48" t="s">
+        <v>421</v>
+      </c>
+      <c r="O48" t="s">
+        <v>422</v>
+      </c>
+      <c r="P48" t="s">
         <v>423</v>
-      </c>
-      <c r="O48" t="s">
-        <v>424</v>
-      </c>
-      <c r="P48" t="s">
-        <v>425</v>
       </c>
       <c r="Q48">
         <v>8</v>
@@ -5258,54 +5174,51 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49">
-        <v>61</v>
-      </c>
       <c r="C49" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E49">
         <v>197</v>
       </c>
       <c r="F49" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G49" t="s">
+        <v>415</v>
+      </c>
+      <c r="H49" t="s">
+        <v>416</v>
+      </c>
+      <c r="I49" t="s">
         <v>417</v>
       </c>
-      <c r="H49" t="s">
-        <v>418</v>
-      </c>
-      <c r="I49" t="s">
+      <c r="J49" t="s">
+        <v>425</v>
+      </c>
+      <c r="K49" t="s">
         <v>419</v>
       </c>
-      <c r="J49" t="s">
-        <v>427</v>
-      </c>
-      <c r="K49" t="s">
-        <v>421</v>
-      </c>
       <c r="L49" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="M49">
         <v>2</v>
       </c>
       <c r="N49" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="O49" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="P49" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="Q49">
         <v>8</v>
@@ -5323,54 +5236,51 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50">
-        <v>60</v>
-      </c>
       <c r="C50" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D50" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E50">
         <v>240</v>
       </c>
       <c r="F50" t="s">
+        <v>427</v>
+      </c>
+      <c r="G50" t="s">
+        <v>34</v>
+      </c>
+      <c r="H50" t="s">
+        <v>428</v>
+      </c>
+      <c r="I50" t="s">
         <v>429</v>
       </c>
-      <c r="G50" t="s">
-        <v>35</v>
-      </c>
-      <c r="H50" t="s">
+      <c r="J50" t="s">
         <v>430</v>
       </c>
-      <c r="I50" t="s">
+      <c r="K50" t="s">
         <v>431</v>
       </c>
-      <c r="J50" t="s">
+      <c r="L50" t="s">
         <v>432</v>
-      </c>
-      <c r="K50" t="s">
-        <v>433</v>
-      </c>
-      <c r="L50" t="s">
-        <v>434</v>
       </c>
       <c r="M50">
         <v>3</v>
       </c>
       <c r="N50" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="O50" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q50">
         <v>27</v>
@@ -5388,54 +5298,51 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51">
-        <v>60</v>
-      </c>
       <c r="C51" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E51">
         <v>261</v>
       </c>
       <c r="F51" t="s">
+        <v>435</v>
+      </c>
+      <c r="G51" t="s">
+        <v>436</v>
+      </c>
+      <c r="H51" t="s">
         <v>437</v>
       </c>
-      <c r="G51" t="s">
+      <c r="I51" t="s">
         <v>438</v>
       </c>
-      <c r="H51" t="s">
+      <c r="J51" t="s">
         <v>439</v>
       </c>
-      <c r="I51" t="s">
+      <c r="K51" t="s">
+        <v>67</v>
+      </c>
+      <c r="L51" t="s">
         <v>440</v>
-      </c>
-      <c r="J51" t="s">
-        <v>441</v>
-      </c>
-      <c r="K51" t="s">
-        <v>68</v>
-      </c>
-      <c r="L51" t="s">
-        <v>442</v>
       </c>
       <c r="M51">
         <v>3</v>
       </c>
       <c r="N51" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="O51" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="P51" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q51">
         <v>15</v>
@@ -5453,54 +5360,51 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52">
-        <v>60</v>
-      </c>
       <c r="C52" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D52" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E52">
         <v>197</v>
       </c>
       <c r="F52" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="G52" t="s">
+        <v>415</v>
+      </c>
+      <c r="H52" t="s">
+        <v>416</v>
+      </c>
+      <c r="I52" t="s">
         <v>417</v>
       </c>
-      <c r="H52" t="s">
-        <v>418</v>
-      </c>
-      <c r="I52" t="s">
+      <c r="J52" t="s">
+        <v>444</v>
+      </c>
+      <c r="K52" t="s">
         <v>419</v>
       </c>
-      <c r="J52" t="s">
-        <v>446</v>
-      </c>
-      <c r="K52" t="s">
-        <v>421</v>
-      </c>
       <c r="L52" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="M52">
         <v>2</v>
       </c>
       <c r="N52" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="O52" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="P52" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="Q52">
         <v>8</v>
@@ -5518,54 +5422,54 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D53" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E53">
         <v>197</v>
       </c>
       <c r="F53" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G53" t="s">
+        <v>415</v>
+      </c>
+      <c r="H53" t="s">
+        <v>416</v>
+      </c>
+      <c r="I53" t="s">
         <v>417</v>
       </c>
-      <c r="H53" t="s">
-        <v>418</v>
-      </c>
-      <c r="I53" t="s">
+      <c r="J53" t="s">
+        <v>447</v>
+      </c>
+      <c r="K53" t="s">
         <v>419</v>
       </c>
-      <c r="J53" t="s">
-        <v>449</v>
-      </c>
-      <c r="K53" t="s">
-        <v>421</v>
-      </c>
       <c r="L53" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="M53">
         <v>2</v>
       </c>
       <c r="N53" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="O53" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="P53" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="Q53">
         <v>8</v>
@@ -5583,54 +5487,51 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54">
-        <v>58</v>
-      </c>
       <c r="C54" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D54" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E54">
         <v>230</v>
       </c>
       <c r="F54" t="s">
+        <v>449</v>
+      </c>
+      <c r="G54" t="s">
+        <v>91</v>
+      </c>
+      <c r="H54" t="s">
+        <v>450</v>
+      </c>
+      <c r="I54" t="s">
         <v>451</v>
       </c>
-      <c r="G54" t="s">
-        <v>92</v>
-      </c>
-      <c r="H54" t="s">
+      <c r="J54" t="s">
         <v>452</v>
       </c>
-      <c r="I54" t="s">
+      <c r="K54" t="s">
+        <v>393</v>
+      </c>
+      <c r="L54" t="s">
         <v>453</v>
-      </c>
-      <c r="J54" t="s">
-        <v>454</v>
-      </c>
-      <c r="K54" t="s">
-        <v>395</v>
-      </c>
-      <c r="L54" t="s">
-        <v>455</v>
       </c>
       <c r="M54">
         <v>3</v>
       </c>
       <c r="N54" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="O54" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="P54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q54">
         <v>32</v>
@@ -5648,54 +5549,51 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55">
-        <v>54</v>
-      </c>
       <c r="C55" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D55" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E55">
         <v>230</v>
       </c>
       <c r="F55" t="s">
+        <v>456</v>
+      </c>
+      <c r="G55" t="s">
+        <v>91</v>
+      </c>
+      <c r="H55" t="s">
+        <v>457</v>
+      </c>
+      <c r="I55" t="s">
         <v>458</v>
       </c>
-      <c r="G55" t="s">
-        <v>92</v>
-      </c>
-      <c r="H55" t="s">
+      <c r="J55" t="s">
         <v>459</v>
       </c>
-      <c r="I55" t="s">
+      <c r="K55" t="s">
         <v>460</v>
       </c>
-      <c r="J55" t="s">
-        <v>461</v>
-      </c>
-      <c r="K55" t="s">
-        <v>462</v>
-      </c>
       <c r="L55" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="M55">
         <v>3</v>
       </c>
       <c r="N55" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="O55" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q55">
         <v>32</v>
@@ -5713,54 +5611,51 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56">
-        <v>52</v>
-      </c>
       <c r="C56" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E56">
         <v>240</v>
       </c>
       <c r="F56" t="s">
+        <v>462</v>
+      </c>
+      <c r="G56" t="s">
+        <v>91</v>
+      </c>
+      <c r="H56" t="s">
+        <v>463</v>
+      </c>
+      <c r="I56" t="s">
         <v>464</v>
       </c>
-      <c r="G56" t="s">
-        <v>92</v>
-      </c>
-      <c r="H56" t="s">
+      <c r="J56" t="s">
         <v>465</v>
       </c>
-      <c r="I56" t="s">
+      <c r="K56" t="s">
         <v>466</v>
       </c>
-      <c r="J56" t="s">
-        <v>467</v>
-      </c>
-      <c r="K56" t="s">
-        <v>468</v>
-      </c>
       <c r="L56" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="M56">
         <v>3</v>
       </c>
       <c r="N56" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="O56" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q56">
         <v>32</v>
@@ -5782,50 +5677,47 @@
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57">
-        <v>50</v>
-      </c>
       <c r="C57" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D57" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E57">
         <v>65</v>
       </c>
       <c r="F57" t="s">
+        <v>469</v>
+      </c>
+      <c r="G57" t="s">
+        <v>91</v>
+      </c>
+      <c r="H57" t="s">
+        <v>470</v>
+      </c>
+      <c r="I57" t="s">
         <v>471</v>
       </c>
-      <c r="G57" t="s">
-        <v>92</v>
-      </c>
-      <c r="H57" t="s">
+      <c r="J57" t="s">
         <v>472</v>
       </c>
-      <c r="I57" t="s">
+      <c r="K57" t="s">
         <v>473</v>
       </c>
-      <c r="J57" t="s">
+      <c r="L57" t="s">
         <v>474</v>
-      </c>
-      <c r="K57" t="s">
-        <v>475</v>
-      </c>
-      <c r="L57" t="s">
-        <v>476</v>
       </c>
       <c r="M57">
         <v>3</v>
       </c>
       <c r="N57" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="O57" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="P57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q57">
         <v>32</v>
@@ -5843,54 +5735,51 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58">
-        <v>48</v>
-      </c>
       <c r="C58" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D58" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E58">
         <v>281</v>
       </c>
       <c r="F58" t="s">
+        <v>476</v>
+      </c>
+      <c r="G58" t="s">
+        <v>23</v>
+      </c>
+      <c r="H58" t="s">
+        <v>477</v>
+      </c>
+      <c r="I58" t="s">
         <v>478</v>
       </c>
-      <c r="G58" t="s">
-        <v>24</v>
-      </c>
-      <c r="H58" t="s">
+      <c r="J58" t="s">
         <v>479</v>
       </c>
-      <c r="I58" t="s">
+      <c r="K58" t="s">
         <v>480</v>
       </c>
-      <c r="J58" t="s">
+      <c r="L58" t="s">
         <v>481</v>
-      </c>
-      <c r="K58" t="s">
-        <v>482</v>
-      </c>
-      <c r="L58" t="s">
-        <v>483</v>
       </c>
       <c r="M58">
         <v>4</v>
       </c>
       <c r="N58" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="O58" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="P58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q58">
         <v>22</v>
@@ -5908,54 +5797,51 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59">
-        <v>45</v>
-      </c>
       <c r="C59" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D59" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E59">
         <v>281</v>
       </c>
       <c r="F59" t="s">
+        <v>485</v>
+      </c>
+      <c r="G59" t="s">
+        <v>91</v>
+      </c>
+      <c r="H59" t="s">
+        <v>486</v>
+      </c>
+      <c r="I59" t="s">
         <v>487</v>
       </c>
-      <c r="G59" t="s">
-        <v>92</v>
-      </c>
-      <c r="H59" t="s">
+      <c r="J59" t="s">
         <v>488</v>
       </c>
-      <c r="I59" t="s">
+      <c r="K59" t="s">
         <v>489</v>
       </c>
-      <c r="J59" t="s">
+      <c r="L59" t="s">
         <v>490</v>
-      </c>
-      <c r="K59" t="s">
-        <v>491</v>
-      </c>
-      <c r="L59" t="s">
-        <v>492</v>
       </c>
       <c r="M59">
         <v>4</v>
       </c>
       <c r="N59" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="O59" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="P59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q59">
         <v>32</v>
@@ -5974,19 +5860,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U59" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="University of Auckland"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:U59" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="J20" r:id="rId1" xr:uid="{64D60B09-2F03-427A-947A-D2309E982655}"/>
+    <hyperlink ref="J15" r:id="rId2" xr:uid="{2955E23F-BEE0-4F5E-99DE-92EA55234BD5}"/>
+    <hyperlink ref="J33" r:id="rId3" xr:uid="{F7783EA5-0852-4202-BE4F-3016D6E8EA76}"/>
+    <hyperlink ref="J48" r:id="rId4" xr:uid="{B296A6C0-9625-464C-878F-566E02DA88C0}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -6006,48 +5889,48 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2">
         <v>230</v>
       </c>
       <c r="C2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E2" t="s">
         <v>497</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>498</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>499</v>
-      </c>
-      <c r="F2" t="s">
-        <v>500</v>
-      </c>
-      <c r="G2" t="s">
-        <v>501</v>
       </c>
     </row>
   </sheetData>
@@ -6067,146 +5950,146 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B5" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B7" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B8" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B9" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B10" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B11" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B12" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B13" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B14" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B15" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B16" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B17" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B18" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
@@ -6226,475 +6109,475 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>523</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C3" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C4" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C5" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B6" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C6" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B7" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C7" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C8" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B9" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C9" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B10" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C10" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C13" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C14" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C15" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B16" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C16" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B17" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C17" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B18" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C18" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B19" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C19" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B20" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C20" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C23" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B24" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C24" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B25" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C25" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B26" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C26" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B27" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C27" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B28" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C28" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B30" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C30" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B31" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C31" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B32" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C32" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C33" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B34" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C34" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B35" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C35" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B36" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C36" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C37" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B38" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C38" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B39" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C39" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B40" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C40" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B41" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C41" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B42" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C42" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B43" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C43" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
   </sheetData>
